--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487607_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487607_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.1956</v>
+        <v>7.5625</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7857</v>
+        <v>5.2071</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4099</v>
+        <v>2.3554</v>
       </c>
       <c r="G2" t="n">
         <v>4.0218</v>
@@ -610,13 +610,13 @@
         <v>2.5224</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2427</v>
+        <v>0.1242</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3903</v>
+        <v>0.8117</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.633</v>
+        <v>-0.6875</v>
       </c>
       <c r="V2" t="n">
         <v>0.894</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2589</v>
+        <v>3.7573</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2988</v>
+        <v>1.8789</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9601</v>
+        <v>1.8784</v>
       </c>
       <c r="G3" t="n">
         <v>2.541</v>
@@ -688,13 +688,13 @@
         <v>2.3284</v>
       </c>
       <c r="S3" t="n">
-        <v>2.8941</v>
+        <v>1.3924</v>
       </c>
       <c r="T3" t="n">
-        <v>3.0719</v>
+        <v>1.652</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1778</v>
+        <v>-0.2596</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5642</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6134</v>
+        <v>2.7041</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1272</v>
+        <v>2.0271</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4862</v>
+        <v>0.677</v>
       </c>
       <c r="G4" t="n">
         <v>1.4668</v>
@@ -766,13 +766,13 @@
         <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5646</v>
+        <v>0.6553</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4374</v>
+        <v>0.3373</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1272</v>
+        <v>0.318</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9795</v>
+        <v>2.3887</v>
       </c>
       <c r="E5" t="n">
-        <v>2.424</v>
+        <v>2.8059</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.4444</v>
+        <v>-0.4172</v>
       </c>
       <c r="G5" t="n">
         <v>-1.1887</v>
@@ -844,13 +844,13 @@
         <v>1.9403</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5034</v>
+        <v>-0.09420000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.4385</v>
+        <v>0.8204</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9419</v>
+        <v>-0.9146</v>
       </c>
       <c r="V5" t="n">
         <v>3.6716</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5896</v>
+        <v>0.717</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6714</v>
+        <v>0.7715</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0818</v>
+        <v>-0.0546</v>
       </c>
       <c r="G6" t="n">
         <v>0.7201</v>
@@ -922,13 +922,13 @@
         <v>0.194</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0424</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0123</v>
+        <v>0.1124</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0547</v>
+        <v>-0.0275</v>
       </c>
       <c r="V6" t="n">
         <v>-0.2821</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4488</v>
+        <v>0.1668</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5019</v>
+        <v>0.3017</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0531</v>
+        <v>-0.1349</v>
       </c>
       <c r="G7" t="n">
         <v>-2.6127</v>
@@ -1000,13 +1000,13 @@
         <v>0.3881</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4495</v>
+        <v>1.1676</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1776</v>
+        <v>0.9774</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2719</v>
+        <v>0.1901</v>
       </c>
       <c r="V7" t="n">
         <v>1.2239</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>D. MAGANTO LUCAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6825</v>
+        <v>-0.8449</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2855</v>
+        <v>-0.6008</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.397</v>
+        <v>-0.2441</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6278</v>
+        <v>-1.109</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.5919</v>
+        <v>0.1211</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0359</v>
+        <v>-1.2301</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.7586</v>
+        <v>-0.335</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.5457</v>
+        <v>0.3501</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2129</v>
+        <v>-0.6851</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.8692</v>
+        <v>-0.774</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0462</v>
+        <v>-0.229</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.545</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>3.0513</v>
+        <v>0.8462</v>
       </c>
       <c r="T9" t="n">
-        <v>2.9374</v>
+        <v>0.7043</v>
       </c>
       <c r="U9" t="n">
-        <v>0.114</v>
+        <v>0.1419</v>
       </c>
       <c r="V9" t="n">
-        <v>0.894</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9453</v>
+        <v>-1.3608</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6695</v>
+        <v>-2.9488</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7242</v>
+        <v>1.588</v>
       </c>
       <c r="G10" t="n">
         <v>-2.4664</v>
@@ -1234,13 +1234,13 @@
         <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2972</v>
+        <v>-0.1183</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0453</v>
+        <v>0.766</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.748</v>
+        <v>-0.8843</v>
       </c>
       <c r="V10" t="n">
         <v>1.2239</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. MAGANTO LUCAS</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.6729</v>
+        <v>-1.9416</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4016</v>
+        <v>-1.6263</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2713</v>
+        <v>-0.3153</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.109</v>
+        <v>-4.6278</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1211</v>
+        <v>-2.5919</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.2301</v>
+        <v>-2.0359</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.335</v>
+        <v>-3.7586</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3501</v>
+        <v>-2.5457</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6851</v>
+        <v>-1.2129</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.774</v>
+        <v>-0.8692</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.229</v>
+        <v>-0.0462</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.545</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3881</v>
+        <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0182</v>
+        <v>1.7923</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0965</v>
+        <v>1.5965</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1146</v>
+        <v>0.1957</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>0.894</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.1222</v>
+        <v>-3.336</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.447</v>
+        <v>-2.8244</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6752</v>
+        <v>-0.5116000000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-3.3164</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.164</v>
+        <v>0.6222</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.005</v>
+        <v>0.6177</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.159</v>
+        <v>0.0045</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2239</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.0328</v>
+        <v>-5.2744</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.7174</v>
+        <v>-5.7955</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6845</v>
+        <v>0.521</v>
       </c>
       <c r="G13" t="n">
         <v>-1.9815</v>
@@ -1468,13 +1468,13 @@
         <v>1.5523</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.7528</v>
+        <v>0.0056</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1592</v>
+        <v>1.0812</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.912</v>
+        <v>-1.0755</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.183499999999997</v>
+        <v>4.0921</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.382500000000001</v>
+        <v>-0.4741</v>
       </c>
       <c r="F14" t="n">
-        <v>4.566</v>
+        <v>4.566000000000002</v>
       </c>
       <c r="G14" t="n">
         <v>-8.0954</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.457899999999999</v>
+        <v>-9.4579</v>
       </c>
       <c r="I14" t="n">
         <v>1.3627</v>
@@ -1522,7 +1522,7 @@
         <v>-5.074599999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>-7.2993</v>
+        <v>-7.299300000000001</v>
       </c>
       <c r="L14" t="n">
         <v>2.2246</v>
@@ -1537,7 +1537,7 @@
         <v>-0.8621000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.9702000000000006</v>
+        <v>0.9701999999999997</v>
       </c>
       <c r="Q14" t="n">
         <v>-13.5823</v>
@@ -1546,13 +1546,13 @@
         <v>14.5525</v>
       </c>
       <c r="S14" t="n">
-        <v>5.035700000000001</v>
+        <v>5.9444</v>
       </c>
       <c r="T14" t="n">
-        <v>8.568399999999999</v>
+        <v>9.476900000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.5326</v>
+        <v>-3.5327</v>
       </c>
       <c r="V14" t="n">
         <v>5.273</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2724</v>
+        <v>4.6165</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9538</v>
+        <v>1.9548</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3186</v>
+        <v>2.6617</v>
       </c>
       <c r="G15" t="n">
         <v>4.2876</v>
@@ -1624,13 +1624,13 @@
         <v>1.7463</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.045</v>
+        <v>-0.701</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.0173</v>
+        <v>-0.0163</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0278</v>
+        <v>-0.6847</v>
       </c>
       <c r="V15" t="n">
         <v>1.2239</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.0647</v>
+        <v>2.8922</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1174</v>
+        <v>2.2175</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9473</v>
+        <v>0.6747</v>
       </c>
       <c r="G16" t="n">
         <v>2.9805</v>
@@ -1702,13 +1702,13 @@
         <v>0.7761</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4722</v>
+        <v>0.2997</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1828</v>
+        <v>0.2829</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2894</v>
+        <v>0.0168</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.8107</v>
+        <v>2.6767</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4955</v>
+        <v>2.7948</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6848</v>
+        <v>-0.1181</v>
       </c>
       <c r="G17" t="n">
         <v>1.5638</v>
@@ -1780,13 +1780,13 @@
         <v>1.1642</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7707000000000001</v>
+        <v>0.6368</v>
       </c>
       <c r="T17" t="n">
-        <v>1.5904</v>
+        <v>0.8897</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8196</v>
+        <v>-0.2529</v>
       </c>
       <c r="V17" t="n">
         <v>0.2821</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>A. SANCHO PEREZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.242</v>
+        <v>0.5119</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0578</v>
+        <v>-0.4122</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1842</v>
+        <v>0.9241</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3205</v>
+        <v>0.7106</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7843</v>
+        <v>1.9864</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4638</v>
+        <v>-1.2757</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2401</v>
+        <v>0.0277</v>
       </c>
       <c r="K18" t="n">
-        <v>0.346</v>
+        <v>1.2811</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5861</v>
+        <v>-1.2535</v>
       </c>
       <c r="M18" t="n">
-        <v>0.5606</v>
+        <v>0.6829</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4383</v>
+        <v>0.7052</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1223</v>
+        <v>-0.0223</v>
       </c>
       <c r="P18" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1642</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0487</v>
+        <v>-0.6152</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8501</v>
+        <v>0.2198</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8988</v>
+        <v>-0.835</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6119</v>
+        <v>-0.9418</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6119</v>
+        <v>-0.6597</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2239</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SANCHO PEREZ</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0786</v>
+        <v>-0.0794</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0118</v>
+        <v>-0.3426</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.2632</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7106</v>
+        <v>0.3205</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9864</v>
+        <v>0.7843</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2757</v>
+        <v>-0.4638</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0277</v>
+        <v>-0.2401</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2811</v>
+        <v>0.346</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.2535</v>
+        <v>-0.5861</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6829</v>
+        <v>0.5606</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7052</v>
+        <v>0.4383</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0223</v>
+        <v>0.1223</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1642</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0485</v>
+        <v>-0.3701</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6202</v>
+        <v>0.4497</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.6687</v>
+        <v>-0.8198</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9418</v>
+        <v>-0.6119</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6597</v>
+        <v>0.6119</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2821</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0071</v>
+        <v>-0.2857</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1729</v>
+        <v>-0.1274</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.18</v>
+        <v>-0.1583</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8922</v>
@@ -2014,13 +2014,13 @@
         <v>0.7761</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7091</v>
+        <v>0.4304</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9354</v>
+        <v>0.6351</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2263</v>
+        <v>-0.2047</v>
       </c>
       <c r="V20" t="n">
         <v>0.5642</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>J. DOMINGUEZ LARRE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.865</v>
+        <v>-0.3718</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0901</v>
+        <v>-0.5335</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2251</v>
+        <v>0.1617</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3781</v>
+        <v>1.1673</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1112</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2669</v>
+        <v>0.2948</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0618</v>
+        <v>0.301</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0618</v>
+        <v>-0.828</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.129</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3164</v>
+        <v>0.8662</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0494</v>
+        <v>1.7004</v>
       </c>
       <c r="O21" t="n">
-        <v>0.2669</v>
+        <v>-0.8342000000000001</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5821</v>
+        <v>0.5821</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-1.1642</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6611</v>
+        <v>-0.8973</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1817</v>
+        <v>0.3297</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4794</v>
+        <v>-1.227</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. DOMINGUEZ LARRE</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9658</v>
+        <v>-0.5497</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5335</v>
+        <v>-0.99</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4323</v>
+        <v>0.4403</v>
       </c>
       <c r="G22" t="n">
-        <v>1.1673</v>
+        <v>0.3781</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8725000000000001</v>
+        <v>0.1112</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2948</v>
+        <v>0.2669</v>
       </c>
       <c r="J22" t="n">
-        <v>0.301</v>
+        <v>0.0618</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.828</v>
+        <v>0.0618</v>
       </c>
       <c r="L22" t="n">
-        <v>1.129</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.8662</v>
+        <v>0.3164</v>
       </c>
       <c r="N22" t="n">
-        <v>1.7004</v>
+        <v>0.0494</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8342000000000001</v>
+        <v>0.2669</v>
       </c>
       <c r="P22" t="n">
-        <v>0.5821</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1642</v>
+        <v>-0.9702</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7463</v>
+        <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.4912</v>
+        <v>-0.3457</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3297</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.821</v>
+        <v>-0.2641</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5694</v>
+        <v>-2.7475</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.0526</v>
+        <v>-3.9525</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4832</v>
+        <v>1.205</v>
       </c>
       <c r="G23" t="n">
         <v>-2.8583</v>
@@ -2248,13 +2248,13 @@
         <v>0.7761</v>
       </c>
       <c r="S23" t="n">
-        <v>0.4352</v>
+        <v>0.2571</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1683</v>
+        <v>-0.0682</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6035</v>
+        <v>0.3253</v>
       </c>
       <c r="V23" t="n">
         <v>0.0478</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3638</v>
+        <v>-3.4884</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1364</v>
+        <v>-3.6369</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.2275</v>
+        <v>0.1485</v>
       </c>
       <c r="G24" t="n">
         <v>-0.58</v>
@@ -2326,13 +2326,13 @@
         <v>1.7463</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4242</v>
+        <v>-0.5487</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0453</v>
+        <v>0.5448</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.4694</v>
+        <v>-1.0935</v>
       </c>
       <c r="V24" t="n">
         <v>-2.1657</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.8808</v>
+        <v>-3.6891</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.539</v>
+        <v>-1.538</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.3419</v>
+        <v>-2.1511</v>
       </c>
       <c r="G25" t="n">
         <v>1.0175</v>
@@ -2404,13 +2404,13 @@
         <v>1.3582</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.7043</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6539</v>
+        <v>0.3471</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0504</v>
+        <v>-0.8597</v>
       </c>
       <c r="V25" t="n">
         <v>-2.4477</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.183499999999998</v>
+        <v>-0.5143</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.566000000000001</v>
+        <v>-4.566</v>
       </c>
       <c r="F26" t="n">
-        <v>1.3823</v>
+        <v>4.0517</v>
       </c>
       <c r="G26" t="n">
         <v>8.0954</v>
@@ -2461,7 +2461,7 @@
         <v>2.158599999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8622999999999995</v>
+        <v>0.8623</v>
       </c>
       <c r="M26" t="n">
         <v>5.0744</v>
@@ -2482,19 +2482,19 @@
         <v>13.5822</v>
       </c>
       <c r="S26" t="n">
-        <v>-5.0358</v>
+        <v>-2.3666</v>
       </c>
       <c r="T26" t="n">
-        <v>3.532699999999999</v>
+        <v>3.5327</v>
       </c>
       <c r="U26" t="n">
-        <v>-8.568499999999998</v>
+        <v>-5.8993</v>
       </c>
       <c r="V26" t="n">
-        <v>-5.273000000000001</v>
+        <v>-5.273</v>
       </c>
       <c r="W26" t="n">
-        <v>3.4328</v>
+        <v>3.432799999999999</v>
       </c>
       <c r="X26" t="n">
         <v>-8.7059</v>
